--- a/99 - Excels/Open-LPs - deitado.xlsx
+++ b/99 - Excels/Open-LPs - deitado.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
@@ -438,265 +426,254 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP-033113</t>
+          <t>LP-039318</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LP-045241</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP-047639</t>
+          <t>LP-048361</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LP-051397</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP-048170</t>
+          <t>LP-051532</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LP-051689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP-051018</t>
+          <t>LP-052355</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP-052552</t>
+          <t>LP-052898</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP-052814</t>
+          <t>LP-053058</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP-052815</t>
+          <t>LP-053250</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP-052816</t>
+          <t>LP-053291</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP-052817</t>
+          <t>LP-053840</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP-052874</t>
+          <t>LP-054013</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP-052931</t>
+          <t>LP-054091</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP-053213</t>
+          <t>LP-054216</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP-053267</t>
+          <t>LP-054273</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP-053270</t>
+          <t>LP-054274</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LP-053485</t>
+          <t>LP-054275</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LP-053497</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LP-053528</t>
+          <t>LP-054396</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LP-053571</t>
+          <t>LP-054471</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LP-053575</t>
+          <t>LP-054862</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LP-053789</t>
+          <t>LP-054939</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LP-053861</t>
+          <t>LP-054947</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LP-053970</t>
+          <t>LP-055005</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LP-054102</t>
+          <t>LP-055141</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LP-054103</t>
+          <t>LP-055183</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LP-054104</t>
+          <t>LP-055298</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LP-054109</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LP-054666</t>
+          <t>LP-055316</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LP-054675</t>
+          <t>LP-055409</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LP-054729</t>
+          <t>LP-055412</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LP-054775</t>
+          <t>LP-055413</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LP-054777</t>
+          <t>LP-055425</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LP-054837</t>
+          <t>LP-055426</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LP-054843</t>
+          <t>LP-055448</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LP-054855</t>
+          <t>LP-055453</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LP-054859</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LP-054882</t>
+          <t>LP-055458</t>
         </is>
       </c>
     </row>

--- a/99 - Excels/Open-LPs - deitado.xlsx
+++ b/99 - Excels/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C97C250-EAB4-401E-BA92-7E96E1E930B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA665DC0-8C5E-4780-9346-059402EAFFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,273 +20,156 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-051534</t>
-  </si>
-  <si>
-    <t>LP-054814</t>
-  </si>
-  <si>
-    <t>LP-053046</t>
-  </si>
-  <si>
-    <t>LP-054923</t>
-  </si>
-  <si>
-    <t>LP-054924</t>
-  </si>
-  <si>
-    <t>LP-056481</t>
-  </si>
-  <si>
-    <t>LP-054464</t>
-  </si>
-  <si>
-    <t>LP-056049</t>
-  </si>
-  <si>
-    <t>LP-054916</t>
-  </si>
-  <si>
-    <t>LP-056093</t>
-  </si>
-  <si>
-    <t>LP-046952</t>
-  </si>
-  <si>
-    <t>LP-056276</t>
-  </si>
-  <si>
-    <t>LP-052184</t>
-  </si>
-  <si>
-    <t>LP-051632</t>
-  </si>
-  <si>
-    <t>LP-055786</t>
-  </si>
-  <si>
-    <t>LP-049613</t>
-  </si>
-  <si>
-    <t>LP-051039</t>
-  </si>
-  <si>
-    <t>LP-056606</t>
-  </si>
-  <si>
-    <t>LP-056773</t>
-  </si>
-  <si>
-    <t>LP-049055</t>
-  </si>
-  <si>
-    <t>LP-050270</t>
-  </si>
-  <si>
-    <t>LP-057039</t>
-  </si>
-  <si>
-    <t>LP-056492</t>
-  </si>
-  <si>
-    <t>LP-056491</t>
-  </si>
-  <si>
-    <t>LP-056530</t>
-  </si>
-  <si>
-    <t>LP-056480</t>
-  </si>
-  <si>
-    <t>LP-057008</t>
-  </si>
-  <si>
-    <t>LP-056998</t>
-  </si>
-  <si>
-    <t>LP-056996</t>
-  </si>
-  <si>
-    <t>LP-056932</t>
-  </si>
-  <si>
-    <t>LP-055245</t>
-  </si>
-  <si>
-    <t>LP-053078</t>
-  </si>
-  <si>
-    <t>LP-056604</t>
-  </si>
-  <si>
-    <t>LP-051398</t>
-  </si>
-  <si>
-    <t>LP-057300</t>
-  </si>
-  <si>
-    <t>LP-055324</t>
-  </si>
-  <si>
-    <t>LP-053048</t>
-  </si>
-  <si>
-    <t>LP-057301</t>
-  </si>
-  <si>
-    <t>LP-057077</t>
-  </si>
-  <si>
-    <t>LP-057572</t>
-  </si>
-  <si>
-    <t>LP-058183</t>
-  </si>
-  <si>
-    <t>LP-058184</t>
-  </si>
-  <si>
-    <t>LP-057136</t>
-  </si>
-  <si>
-    <t>LP-055616</t>
-  </si>
-  <si>
-    <t>LP-056929</t>
-  </si>
-  <si>
-    <t>LP-056261</t>
-  </si>
-  <si>
-    <t>LP-055964</t>
-  </si>
-  <si>
-    <t>LP-056921</t>
-  </si>
-  <si>
-    <t>LP-057693</t>
-  </si>
-  <si>
-    <t>LP-057260</t>
-  </si>
-  <si>
-    <t>LP-057035</t>
-  </si>
-  <si>
-    <t>LP-058330</t>
-  </si>
-  <si>
-    <t>LP-058093</t>
-  </si>
-  <si>
-    <t>LP-057480</t>
-  </si>
-  <si>
-    <t>LP-057445</t>
-  </si>
-  <si>
-    <t>LP-058181</t>
-  </si>
-  <si>
-    <t>LP-058092</t>
-  </si>
-  <si>
-    <t>LP-057866</t>
-  </si>
-  <si>
-    <t>LP-057978</t>
-  </si>
-  <si>
-    <t>LP-057088</t>
-  </si>
-  <si>
-    <t>LP-057079</t>
-  </si>
-  <si>
-    <t>LP-058185</t>
-  </si>
-  <si>
-    <t>LP-057386</t>
-  </si>
-  <si>
-    <t>LP-057184</t>
-  </si>
-  <si>
-    <t>LP-056956</t>
-  </si>
-  <si>
-    <t>LP-057529</t>
-  </si>
-  <si>
-    <t>LP-057291</t>
-  </si>
-  <si>
-    <t>LP-057697</t>
-  </si>
-  <si>
-    <t>LP-057769</t>
-  </si>
-  <si>
-    <t>LP-057106</t>
-  </si>
-  <si>
-    <t>LP-057107</t>
-  </si>
-  <si>
-    <t>LP-057595</t>
-  </si>
-  <si>
-    <t>LP-057289</t>
-  </si>
-  <si>
-    <t>LP-057882</t>
-  </si>
-  <si>
-    <t>LP-056912</t>
-  </si>
-  <si>
-    <t>LP-057850</t>
-  </si>
-  <si>
-    <t>LP-058178</t>
-  </si>
-  <si>
-    <t>LP-057381</t>
-  </si>
-  <si>
-    <t>LP-057592</t>
-  </si>
-  <si>
-    <t>LP-056777</t>
-  </si>
-  <si>
-    <t>LP-043234</t>
-  </si>
-  <si>
-    <t>LP-055118</t>
-  </si>
-  <si>
-    <t>LP-058190</t>
-  </si>
-  <si>
-    <t>LP-057306</t>
-  </si>
-  <si>
-    <t>LP-057907</t>
-  </si>
-  <si>
-    <t>LP-054355</t>
-  </si>
-  <si>
-    <t>LP-058172</t>
-  </si>
-  <si>
-    <t>LP-056731</t>
+    <t>LP-045438</t>
+  </si>
+  <si>
+    <t>LP-045668</t>
+  </si>
+  <si>
+    <t>LP-045931</t>
+  </si>
+  <si>
+    <t>LP-051052</t>
+  </si>
+  <si>
+    <t>LP-052741</t>
+  </si>
+  <si>
+    <t>LP-055210</t>
+  </si>
+  <si>
+    <t>LP-055787</t>
+  </si>
+  <si>
+    <t>LP-055791</t>
+  </si>
+  <si>
+    <t>LP-055898</t>
+  </si>
+  <si>
+    <t>LP-056004</t>
+  </si>
+  <si>
+    <t>LP-056255</t>
+  </si>
+  <si>
+    <t>LP-056580</t>
+  </si>
+  <si>
+    <t>LP-056612</t>
+  </si>
+  <si>
+    <t>LP-056613</t>
+  </si>
+  <si>
+    <t>LP-055790</t>
+  </si>
+  <si>
+    <t>LP-056796</t>
+  </si>
+  <si>
+    <t>LP-056802</t>
+  </si>
+  <si>
+    <t>LP-056879</t>
+  </si>
+  <si>
+    <t>LP-056914</t>
+  </si>
+  <si>
+    <t>LP-056927</t>
+  </si>
+  <si>
+    <t>LP-056939</t>
+  </si>
+  <si>
+    <t>LP-056955</t>
+  </si>
+  <si>
+    <t>LP-057084</t>
+  </si>
+  <si>
+    <t>LP-057086</t>
+  </si>
+  <si>
+    <t>LP-057104</t>
+  </si>
+  <si>
+    <t>LP-057105</t>
+  </si>
+  <si>
+    <t>LP-057119</t>
+  </si>
+  <si>
+    <t>LP-057175</t>
+  </si>
+  <si>
+    <t>LP-057258</t>
+  </si>
+  <si>
+    <t>LP-057276</t>
+  </si>
+  <si>
+    <t>LP-057364</t>
+  </si>
+  <si>
+    <t>LP-057453</t>
+  </si>
+  <si>
+    <t>LP-057454</t>
+  </si>
+  <si>
+    <t>LP-057556</t>
+  </si>
+  <si>
+    <t>LP-057602</t>
+  </si>
+  <si>
+    <t>LP-057665</t>
+  </si>
+  <si>
+    <t>LP-057724</t>
+  </si>
+  <si>
+    <t>LP-057809</t>
+  </si>
+  <si>
+    <t>LP-057839</t>
+  </si>
+  <si>
+    <t>LP-057919</t>
+  </si>
+  <si>
+    <t>LP-058088</t>
+  </si>
+  <si>
+    <t>LP-058121</t>
+  </si>
+  <si>
+    <t>LP-058163</t>
+  </si>
+  <si>
+    <t>LP-058278</t>
+  </si>
+  <si>
+    <t>LP-058366</t>
+  </si>
+  <si>
+    <t>LP-058368</t>
+  </si>
+  <si>
+    <t>LP-058473</t>
+  </si>
+  <si>
+    <t>LP-056071</t>
+  </si>
+  <si>
+    <t>LP-057438</t>
   </si>
 </sst>
 </file>
@@ -626,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A89"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -686,392 +569,197 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
